--- a/Plan_90_Dias_Dir_Mtto_Transpais.xlsx
+++ b/Plan_90_Dias_Dir_Mtto_Transpais.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbd5ad93608ef24b/2. Planes 90 Días/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cbd5ad93608ef24b/2. Planes 90 Días/Plan Dir Mantto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2487" documentId="8_{21D8742F-BBFF-42A5-9AD3-D3DF45B525E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BA198C4-6D0C-4642-AE49-584F60E461F9}"/>
+  <xr:revisionPtr revIDLastSave="2490" documentId="8_{21D8742F-BBFF-42A5-9AD3-D3DF45B525E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B08101D3-6389-4794-8D93-C5A553C17AB5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6327,10 +6327,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6673,7 +6669,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.5703125" bestFit="1" customWidth="1"/>
@@ -7243,13 +7239,14 @@
         <v>507</v>
       </c>
     </row>
-    <row r="42" spans="1:5" s="248" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:5" s="248" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" s="248" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:5" s="248" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="D43" s="248">
         <f>8*0.95</f>
         <v>7.6</v>
       </c>
     </row>
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -7257,6 +7254,8 @@
         <v>508</v>
       </c>
     </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="49" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A28:E28"/>
@@ -11574,7 +11573,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{5692DF4B-3895-4A9E-A029-DB7E8A532DAD}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{9454FB64-9499-4555-9AEC-1B9C4D54CE12}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -11585,8 +11584,196 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D34:Q34</xm:f>
-              <xm:sqref>U34</xm:sqref>
+              <xm:f>'Benchmark KPIs Corp'!D37:Q37</xm:f>
+              <xm:sqref>U37</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{85940606-A699-4EF8-AF2E-F72645112ACE}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D35:Q35</xm:f>
+              <xm:sqref>U35</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D36:Q36</xm:f>
+              <xm:sqref>U36</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{FD58BD14-DD54-405D-AFB8-16435181DA86}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D32:Q32</xm:f>
+              <xm:sqref>U32</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D33:Q33</xm:f>
+              <xm:sqref>U33</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{1BFFB6D1-4C10-49A5-AAEA-216934FFEC4B}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D30:Q30</xm:f>
+              <xm:sqref>U30</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D31:Q31</xm:f>
+              <xm:sqref>U31</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{52F2249D-2044-4656-B4CE-D79095D54F7E}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D26:Q26</xm:f>
+              <xm:sqref>U26</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D27:Q27</xm:f>
+              <xm:sqref>U27</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D28:Q28</xm:f>
+              <xm:sqref>U28</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D29:Q29</xm:f>
+              <xm:sqref>U29</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3F7C8C12-916C-4E41-AD9F-65CAEFEFF9A0}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D22:Q22</xm:f>
+              <xm:sqref>U22</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D23:Q23</xm:f>
+              <xm:sqref>U23</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D24:Q24</xm:f>
+              <xm:sqref>U24</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D25:Q25</xm:f>
+              <xm:sqref>U25</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{AE6C977C-0CAE-48F5-A0C5-811C849832DE}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D18:Q18</xm:f>
+              <xm:sqref>U18</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D19:Q19</xm:f>
+              <xm:sqref>U19</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D20:Q20</xm:f>
+              <xm:sqref>U20</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D21:Q21</xm:f>
+              <xm:sqref>U21</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{C74C6909-30B4-49EB-A7EA-541734F2FA37}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D14:Q14</xm:f>
+              <xm:sqref>U14</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D15:Q15</xm:f>
+              <xm:sqref>U15</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D16:Q16</xm:f>
+              <xm:sqref>U16</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D17:Q17</xm:f>
+              <xm:sqref>U17</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{725BCB76-3027-4731-B16E-392F861F8199}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Corp'!D3:Q3</xm:f>
+              <xm:sqref>U3</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -11642,7 +11829,7 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{725BCB76-3027-4731-B16E-392F861F8199}">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{5692DF4B-3895-4A9E-A029-DB7E8A532DAD}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
           <x14:colorAxis rgb="FF000000"/>
@@ -11653,196 +11840,8 @@
           <x14:colorLow rgb="FFD00000"/>
           <x14:sparklines>
             <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D3:Q3</xm:f>
-              <xm:sqref>U3</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{C74C6909-30B4-49EB-A7EA-541734F2FA37}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D14:Q14</xm:f>
-              <xm:sqref>U14</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D15:Q15</xm:f>
-              <xm:sqref>U15</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D16:Q16</xm:f>
-              <xm:sqref>U16</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D17:Q17</xm:f>
-              <xm:sqref>U17</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{AE6C977C-0CAE-48F5-A0C5-811C849832DE}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D18:Q18</xm:f>
-              <xm:sqref>U18</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D19:Q19</xm:f>
-              <xm:sqref>U19</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D20:Q20</xm:f>
-              <xm:sqref>U20</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D21:Q21</xm:f>
-              <xm:sqref>U21</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{3F7C8C12-916C-4E41-AD9F-65CAEFEFF9A0}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D22:Q22</xm:f>
-              <xm:sqref>U22</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D23:Q23</xm:f>
-              <xm:sqref>U23</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D24:Q24</xm:f>
-              <xm:sqref>U24</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D25:Q25</xm:f>
-              <xm:sqref>U25</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{52F2249D-2044-4656-B4CE-D79095D54F7E}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D26:Q26</xm:f>
-              <xm:sqref>U26</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D27:Q27</xm:f>
-              <xm:sqref>U27</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D28:Q28</xm:f>
-              <xm:sqref>U28</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D29:Q29</xm:f>
-              <xm:sqref>U29</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{1BFFB6D1-4C10-49A5-AAEA-216934FFEC4B}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D30:Q30</xm:f>
-              <xm:sqref>U30</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D31:Q31</xm:f>
-              <xm:sqref>U31</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{FD58BD14-DD54-405D-AFB8-16435181DA86}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D32:Q32</xm:f>
-              <xm:sqref>U32</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D33:Q33</xm:f>
-              <xm:sqref>U33</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{85940606-A699-4EF8-AF2E-F72645112ACE}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D35:Q35</xm:f>
-              <xm:sqref>U35</xm:sqref>
-            </x14:sparkline>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D36:Q36</xm:f>
-              <xm:sqref>U36</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{9454FB64-9499-4555-9AEC-1B9C4D54CE12}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Corp'!D37:Q37</xm:f>
-              <xm:sqref>U37</xm:sqref>
+              <xm:f>'Benchmark KPIs Corp'!D34:Q34</xm:f>
+              <xm:sqref>U34</xm:sqref>
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
@@ -12527,22 +12526,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{9CA5B189-4613-4D7E-90D6-B02F4CC937B9}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>'Benchmark KPIs Op'!B3:M3</xm:f>
-              <xm:sqref>Q3</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{473DB093-DB64-4F76-BFFF-9294AB2CC3C4}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
@@ -12595,6 +12578,22 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{9CA5B189-4613-4D7E-90D6-B02F4CC937B9}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'Benchmark KPIs Op'!B3:M3</xm:f>
+              <xm:sqref>Q3</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
       </x14:sparklineGroups>
     </ext>
   </extLst>
